--- a/ejemplos/Ejemplo_simpodico.xlsx
+++ b/ejemplos/Ejemplo_simpodico.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +63,9 @@
       <name val="Arial"/>
       <i val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -109,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -141,6 +144,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -52648,11 +52652,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -52762,6 +52767,11 @@
           <t>Altura promedio por especie (sección 2)</t>
         </is>
       </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Función de volumen (sección 2)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -52772,6 +52782,11 @@
       <c r="B14" s="16" t="n">
         <v>7</v>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Compendio N° 111 (Peumo-Maqui), asignada por similitud: la especie no tiene función en el compendio</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -52782,6 +52797,11 @@
       <c r="B15" s="16" t="n">
         <v>5.5</v>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Compendio N° 111 (Peumo-Maqui), asignada por similitud: la especie no tiene función en el compendio</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -52792,6 +52812,11 @@
       <c r="B16" s="16" t="n">
         <v>8</v>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Compendio N° 111 (Peumo-Maqui), automática</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -52802,6 +52827,11 @@
       <c r="B17" s="16" t="n">
         <v>6</v>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Compendio N° 111 (Peumo-Maqui), asignada por similitud: la especie no tiene función en el compendio</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -52812,6 +52842,11 @@
       <c r="B18" s="16" t="n">
         <v>4</v>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Compendio N° 111 (Peumo-Maqui), asignada por similitud: la especie no tiene función en el compendio</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -52821,6 +52856,11 @@
       </c>
       <c r="B19" s="16" t="n">
         <v>10</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Compendio N° 111 (Peumo-Maqui), asignada por similitud: la especie no tiene función en el compendio</t>
+        </is>
       </c>
     </row>
     <row r="21">

--- a/ejemplos/Ejemplo_simpodico.xlsx
+++ b/ejemplos/Ejemplo_simpodico.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ficha predial" sheetId="6" state="visible" r:id="rIdFicha"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parámetros del ejemplo" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="4" state="visible" r:id="rId4"/>
@@ -57411,4 +57412,116 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheetFicha.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Ficha predial</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Campo</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Nombre del predio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Hijuela El Peumal (ejemplo ficticio)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Rol de avalúo</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>789-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Región</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Quillota</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Comuna</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Hijuelas</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Propietario</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Propietaria de ejemplo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Antecedentes ficticios del ejemplo: no corresponden a un predio ni a personas reales.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>